--- a/download/ui-kit-checklist.xlsx
+++ b/download/ui-kit-checklist.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Components" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infrastructure" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Компоненты" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфраструктура" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,21 @@
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
+      <color rgb="001B7D46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,22 +82,12 @@
     </font>
     <font>
       <name val="Noto Sans CJK SC"/>
-      <color rgb="001B7D46"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Noto Sans CJK SC"/>
       <b val="1"/>
       <color rgb="00795548"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -101,17 +106,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,39 +167,46 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -563,59 +580,59 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>@stsgs/ui -- Checklist of Components</t>
+          <t>@stsgs/ui -- Чеклист компонентов</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Updated: 2026-05-13 | Legend: DONE = done, WIP = in progress, TODO = not started, SKIP = intentionally skipped</t>
+          <t>Обновлено: 13.05.2026  |  Статусы: DONE = готово, WIP = в работе, TODO = не начато, SKIP = пропущено</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Компонент</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Слой</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Источник</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Lines</t>
+          <t>Строк</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Описание</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sections (Layer 3) -- Page Sections</t>
+          <t>Секции (Layer 3) -- Блоки страниц</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -630,19 +647,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>hero-section</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -650,9 +667,9 @@
           <t>120</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Hero with variants</t>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Главный экран с вариантами</t>
         </is>
       </c>
     </row>
@@ -662,19 +679,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>navbar-section</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -682,9 +699,9 @@
           <t>95</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Nav bar</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Навигационная панель</t>
         </is>
       </c>
     </row>
@@ -694,19 +711,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>footer-section</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -714,9 +731,9 @@
           <t>85</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Footer</t>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Подвал сайта</t>
         </is>
       </c>
     </row>
@@ -726,19 +743,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>cta-section</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -746,9 +763,9 @@
           <t>78</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Call to action</t>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Призыв к действию</t>
         </is>
       </c>
     </row>
@@ -758,19 +775,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>faq-section</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -778,9 +795,9 @@
           <t>83</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Accordion + grid</t>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Аккордеон + сетка</t>
         </is>
       </c>
     </row>
@@ -790,19 +807,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>testimonials-section</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -810,9 +827,9 @@
           <t>119</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Grid + masonry, stars</t>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Сетка + масонри, звёзды</t>
         </is>
       </c>
     </row>
@@ -822,19 +839,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>stats-section</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -842,9 +859,9 @@
           <t>97</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Row + grid + compact</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Ряд + сетка + компакт</t>
         </is>
       </c>
     </row>
@@ -854,19 +871,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>features-section</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -874,9 +891,9 @@
           <t>121</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Grid + list + bento</t>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Сетка + список + бенто</t>
         </is>
       </c>
     </row>
@@ -886,19 +903,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>pricing-cards</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -906,9 +923,9 @@
           <t>100</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Tier cards</t>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Карточки тарифов</t>
         </is>
       </c>
     </row>
@@ -918,19 +935,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>contact-section</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -938,9 +955,9 @@
           <t>101</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Centered + split</t>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>По центру + сплит</t>
         </is>
       </c>
     </row>
@@ -950,19 +967,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>logo-cloud</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -970,9 +987,9 @@
           <t>77</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Grayscale toggle</t>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Оттенки серого</t>
         </is>
       </c>
     </row>
@@ -982,19 +999,19 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>newsletter-section</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>new (Wave 1)</t>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>новый (Волна 1)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1002,16 +1019,16 @@
           <t>83</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Default + compact + banner</t>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Стандарт + компакт + баннер</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>UI Controls (Layer 2) -- Extracted from repos</t>
+          <t>UI-контролы (Layer 2) -- Извлечено из репо</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
@@ -1026,29 +1043,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>slider-control</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Label + value + range</t>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Ползунок с подписью и значением</t>
         </is>
       </c>
     </row>
@@ -1058,29 +1075,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>color-picker-input</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Picker + hex + presets</t>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Пикер + hex-ввод + пресеты</t>
         </is>
       </c>
     </row>
@@ -1090,29 +1107,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>copy-button</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Copy with check feedback</t>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Копирование с галочкой</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1139,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>code-block</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>VS Code chrome + lines</t>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>VS Code хром + номера строк</t>
         </is>
       </c>
     </row>
@@ -1154,36 +1171,36 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>force-graph</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Physics graph (6 files)</t>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Физический граф (6 файлов)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Features (Layer 4) -- Interactive Widgets</t>
+          <t>Фичи (Layer 4) -- Интерактивные виджеты</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
@@ -1198,29 +1215,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>floating-decorations</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>CSS-only floating symbols</t>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Плавающие символы (CSS, без фреймворков)</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1247,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>scroll-progress-bar</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Fixed top bar</t>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Фиксированная полоса прогресса</t>
         </is>
       </c>
     </row>
@@ -1262,29 +1279,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>activity-timeline</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Vertical timeline</t>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Вертикальная лента событий</t>
         </is>
       </c>
     </row>
@@ -1294,29 +1311,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>command-palette</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Cmd+K palette</t>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Палитра команд Cmd+K</t>
         </is>
       </c>
     </row>
@@ -1326,29 +1343,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>ide-layout</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>IDE shell</t>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Оболочка IDE</t>
         </is>
       </c>
     </row>
@@ -1358,29 +1375,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>responsive-showcase</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>Responsive preview</t>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Адаптивный превью</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1407,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>search-panel</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Search panel</t>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Панель поиска</t>
         </is>
       </c>
     </row>
@@ -1422,36 +1439,36 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>theme-toggle</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Theme switch</t>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Переключатель темы</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Hooks (Layer 5)</t>
+          <t>Хуки (Layer 5)</t>
         </is>
       </c>
       <c r="B36" s="5" t="n"/>
@@ -1466,29 +1483,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>use-mounted</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>SSR-safe mount check</t>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>SSR-безопасная проверка монтирования</t>
         </is>
       </c>
     </row>
@@ -1498,29 +1515,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>use-copy-to-clipboard</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Clipboard + fallback</t>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Буфер обмена + фоллбэк</t>
         </is>
       </c>
     </row>
@@ -1530,29 +1547,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>use-animated-counter</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>rAF number animation</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Анимация чисел через rAF</t>
         </is>
       </c>
     </row>
@@ -1562,29 +1579,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>use-scroll-progress</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Scroll % + isScrolled</t>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Прогресс скролла + isScrolled</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1611,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>use-local-storage</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Reactive localStorage</t>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Реактивный localStorage</t>
         </is>
       </c>
     </row>
@@ -1626,29 +1643,29 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>use-breakpoint</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>оригинал</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>isMobile/isTablet/isDesktop</t>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>isMobile / isTablet / isDesktop</t>
         </is>
       </c>
     </row>
@@ -1658,36 +1675,36 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>use-graph-highlight</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Connected edges/nodes</t>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Подсветка связей при наведении</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>TODO: Remaining Extractable -- Code-Realm + Component-Browser</t>
+          <t>TODO: Остальные компоненты из Code-Realm и Component-Browser</t>
         </is>
       </c>
       <c r="B45" s="5" t="n"/>
@@ -1697,489 +1714,489 @@
       <c r="F45" s="5" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>compare-slider</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>~120</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Before/after image slider</t>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Слайдер до/после для изображений</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>error-boundary</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>~80</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>React error boundary</t>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Обработка ошибок React</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>sound-toggle</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>~50</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>Mute/unmute with icon</t>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Выкл/вкл звука с иконкой</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>preset-grid</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>~60</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>Grid of preset options</t>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Сетка пресет-опций</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>info-bar</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>~40</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Info footer bar</t>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Информационная панель снизу</t>
         </is>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>section-header</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>~50</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Title + subtitle + badge</t>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Заголовок + подзаголовок + бейдж</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>format-tabs</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>~40</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>CSS/JS/JSON format tabs</t>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Табы CSS/JS/JSON</t>
         </is>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>floating-particles</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Code-Realm</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>~100</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>Canvas particles</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Частицы на Canvas</t>
         </is>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>stats-dashboard</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>~200</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>Metrics dashboard (split)</t>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Дашборд с метриками (нужно разбить)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>compare-modal</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>~120</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>Side-by-side modal</t>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Модалка сравнения бок о бок</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>code-viewer-modal</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>~100</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>Code in modal</t>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Код в модалке</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>keyboard-help-modal</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>~80</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Keyboard shortcuts</t>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Горячие клавиши</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>search-history-dropdown</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>~60</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>Search suggestions</t>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Выпадающая история поиска</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>component-card</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>~70</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Component preview card</t>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Карточка превью компонента</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>use-keyboard-shortcuts</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>hooks</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>Component-Browser</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>~50</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>Global key bindings</t>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Глобальные сочетания клавиш</t>
         </is>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>SKIP -- Intentionally Not Extracted</t>
+          <t>SKIP -- Намеренно не извлекалось</t>
         </is>
       </c>
       <c r="B62" s="5" t="n"/>
@@ -2189,98 +2206,98 @@
       <c r="F62" s="5" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>toggle-group</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>shadcn exists</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>есть в shadcn</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Already in shadcn/ui</t>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Уже есть в shadcn/ui</t>
         </is>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>section-shell</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>ui</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>too specific</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>слишком специфичн.</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>Per-project customization</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Нужна кастомизация под проект</t>
         </is>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>24 monolith sections</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>24 монолитных секции</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>sections</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>too hardcoded</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>всё захардкожено</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>All hardcoded content</t>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Захардкоженный контент</t>
         </is>
       </c>
     </row>
@@ -2310,307 +2327,307 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Git Checklist</t>
+          <t>Инфраструктура и Git</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Статус</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Задача</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Детали</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Priority</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+          <t>Приоритет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Git push на GitHub</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>9 локальных коммитов запушены: c87b27c..590609f. Репо: stsgs1980/UI-Kit.git</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>ВЫПОЛНЕНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>WIP</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Git push to GitHub</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>9 local commits not pushed. Remote: stsgs1980/UI-Kit.git. No GitHub token in sandbox -- YOU need to push manually from your machine.</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>GitHub PAT setup</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>PAT was revoked during earlier session. Re-created but not saved in sandbox. Configure locally.</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Отзыв GitHub PAT</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Токен был в чате -- отзови его! Settings &gt; Developer settings &gt; PAT &gt; Delete. Создай новый при необходимости.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+          <t>СРОЧНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>GitHub Actions CI</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>No CI pipeline yet. Add .github/workflows/ for lint + tsc + build on push.</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Нет CI-пайплайна. Добавить .github/workflows/: lint + tsc + build при push.</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>СРЕДНИЙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ESLint plugin update</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>eslint-plugin-stsgs has 4 rules (no-unicode, no-hardcoded-colors, no-direct-import, layer-check). May need Rule 1 enforcement.</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Обновление ESLint-плагина</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>eslint-plugin-stsgs: 4 правила (no-unicode, no-hardcoded-colors, no-direct-import, layer-check). Можно добавить Rule 1 (лимиты строк).</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Anti-monolith compliance</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>All files pass Rule 1 (&lt;=150 lines). 0 violations.</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>TypeScript strict mode</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>tsc --noEmit = 0 errors in src/ (only template file errors in docs/)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Dual Theme System</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Studio + Project theme providers. 5 presets. Champagne default.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+          <t>НИЗКИЙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Анти-монолит аудит</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Все файлы проходят Rule 1 (&lt;=150 строк). 0 нарушений.</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>ВЫПОЛНЕНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>TypeScript strict</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>tsc --noEmit = 0 ошибок в src/. Только шаблонные ошибки в docs/templates/.</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>ВЫПОЛНЕНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Двойная система тем</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Studio + Project провайдеры. 5 пресетов. Champagne -- по умолчанию.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>ВЫПОЛНЕНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Layout Engine</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>51 recipes, scoring, multi-goal support. DONE.</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>51 рецепт, скоринг, мульти-цели. ГОТОВ.</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>ВЫПОЛНЕНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Theme Engine</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Registry, per-file presets, CSS variables. DONE.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Реестр, пресеты по файлам, CSS-переменные. ГОТОВ.</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>ВЫПОЛНЕНО</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Component Engine</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Phase 4b -- DEFERRED. Blocked: needs critical mass of components first.</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Фаза 4b -- ОТЛОЖЕНА. Блокер: нужна критическая масса компонентов.</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>СРЕДНИЙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>recommendTheme()</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>AI-powered theme recommendation based on context/audience. Future.</t>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>AI-рекомендация темы на основе контекста/аудитории. Будущее.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+          <t>НИЗКИЙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Unified Studio Flow</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Single UI combining Layout + Theme + Component engines. Future.</t>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Единый UI: Layout + Theme + Component движки вместе. Будущее.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+          <t>НИЗКИЙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>GIT PUSH: No GitHub token in sandbox. You must push manually: cd UI-Kit &amp;&amp; git push origin main</t>
+          <t>ВНИМАНИЕ: GitHub PAT был в истории чата. Немедленно отзовите и создайте новый токен!</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -2636,15 +2653,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Summary Dashboard</t>
+          <t>Сводная панель</t>
         </is>
       </c>
     </row>
@@ -2652,147 +2669,140 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Категория</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Remaining</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr"/>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Sections (Layer 3)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
+          <t>Осталось</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Секции (Layer 3)</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr"/>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>UI Controls (Layer 2)</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>UI-контролы (Layer 2)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Features (Layer 4)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Фичи (Layer 4)</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="8" t="inlineStr"/>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Hooks (Layer 5)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Хуки (Layer 5)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Total Components</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>ИТОГО компонентов</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="D8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="17" t="inlineStr"/>
+      <c r="B9" s="17" t="inlineStr"/>
+      <c r="C9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Инфраструктура</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Engines (Layout/Theme/Component)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>2 done, 1 deferred</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Движки (Layout/Theme/Comp)</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>2 готово, 1 отложен</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
